--- a/output/satyam_7d.xlsx
+++ b/output/satyam_7d.xlsx
@@ -8035,7 +8035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -8120,11 +8120,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C:52.0, AS:52.0, AD:52.0</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
+          <t>C:49.0, AS:49.0, AD:49.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -8140,7 +8142,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -8148,11 +8150,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C:467948.0, AS:467948.0, AD:467948.0</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
+          <t>C:440951.0, AS:440951.0, AD:440951.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mismatch</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -8425,6 +8429,422 @@
       <c r="F14" t="inlineStr">
         <is>
           <t>Count of sales that still lack a valid sale date</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>G. Total Sales</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>52</v>
+      </c>
+      <c r="D15" t="n">
+        <v>52</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>G. Attributed Sales</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" t="n">
+        <v>49</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>G. Unattributed Sales</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Sales</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>G. Total Revenue</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="D18" t="n">
+        <v>467948</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>G. Attributed Revenue</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="D19" t="n">
+        <v>440951</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>G. Unattributed Revenue</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>26997</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unattributed Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>G. Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>456047.55</v>
+      </c>
+      <c r="D21" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="E21" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Raw Meta Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>G. Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="D22" t="n">
+        <v>282120.59</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Attributed Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>G. Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>173926.96</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Unallocated Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. Profit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="D24" t="n">
+        <v>158830.41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Golden Report verification for Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>G. ROAS</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>G. ROI %</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Golden Report verification for ROI %</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>G. CAC</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5757.56</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Golden Report verification for CAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INV. Revenue Formula</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Attributed + Unattributed = Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>INV. Spend Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Attributed + Unallocated = Raw Spend</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INV. Profit Formula</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Attributed Revenue - Attributed Spend = Profit</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -14529,7 +14949,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>foremost leads | cbo | 11th august 2026</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Primary</t>
@@ -14539,26 +14963,22 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3.125</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -14584,7 +15004,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026</t>
+          <t>foremost leads | cbo | 14th august</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -14596,16 +15016,20 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>3.125</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H7" s="2" t="n">
         <v>8999</v>
@@ -14637,7 +15061,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august</t>
+          <t>--</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -14649,26 +15073,22 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -14687,7 +15107,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
@@ -15431,7 +15851,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fml-p1-002 – copy _ cprg</t>
+          <t>foremost leads &lt;&gt; 2103</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -15488,7 +15908,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103</t>
+          <t>foremost leads &lt;&gt; 2103 cbo s2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -15545,7 +15965,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo s2</t>
+          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -15602,7 +16022,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s2</t>
+          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -15659,7 +16079,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 2103 cbo lla &lt;&gt; s3</t>
+          <t>fml-p1-002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -15671,20 +16091,16 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>0</v>
@@ -15716,7 +16132,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; cc297623 | images</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -15728,16 +16144,20 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="4" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H27" s="2" t="n">
         <v>0</v>
@@ -15769,7 +16189,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; cc297623 | images</t>
+          <t>foremost leads &lt;&gt; ry &lt;&gt; 11/06 &lt;&gt; abo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -15826,7 +16246,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; ry &lt;&gt; 11/06 &lt;&gt; abo</t>
+          <t>foremost leads | cbo | 5th aug 2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -15838,20 +16258,16 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>68</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>0</v>
@@ -15883,7 +16299,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026</t>
+          <t>foremostleads + rky+ 09/04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -15895,16 +16311,20 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>68</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="4" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H30" s="2" t="n">
         <v>0</v>
@@ -15936,7 +16356,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 09/04</t>
+          <t>foremostleads + rky+ 19/04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -15993,7 +16413,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 19/04</t>
+          <t>foremostleads + rky+ 22/04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -16050,7 +16470,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremostleads + rky+ 22/04</t>
+          <t>foremostleads-gs-13-09 7 video ads</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -16107,7 +16527,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 7 video ads</t>
+          <t>foremostleads-gs-13-09- simple image ads</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -16164,7 +16584,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09- simple image ads</t>
+          <t>foremostleads-gs-13-09-10-video ads</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -16221,7 +16641,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09-10-video ads</t>
+          <t>formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -16278,7 +16698,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>formost leads &lt;&gt; video &lt;&gt; talking head &lt;&gt; cbo | 74852</t>
+          <t>new leads campaign</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16335,7 +16755,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>new leads campaign</t>
+          <t>retargeting-campaign [22-12-25]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16392,7 +16812,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>retargeting-campaign [22-12-25]</t>
+          <t>fml-p1-002 – copy _ cprg</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -16449,7 +16869,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>fml-p1-002</t>
+          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -16461,16 +16881,20 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F40" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="4" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H40" s="2" t="n">
         <v>0</v>
@@ -16502,7 +16926,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>fml-cprg-cbo-p1 [12-12-25] cprg</t>
+          <t>chatgpt.com</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -16514,20 +16938,16 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>0</v>
@@ -16559,7 +16979,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>fml-cbo-test – copy</t>
+          <t>fml-am1-abo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -16616,7 +17036,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fml-am-abo-campaign</t>
+          <t>fml-c1-broad - travel interests</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -17015,7 +17435,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>fml-am1-abo</t>
+          <t>fml-am-abo-campaign</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -17072,7 +17492,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fml-abo-c2</t>
+          <t>fml-cbo-test – copy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -17129,7 +17549,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fml-cbo-test</t>
+          <t>fml-abo-c2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -17528,7 +17948,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>chatgpt.com</t>
+          <t>fml-c1-broad - travel interests – copy</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -17540,16 +17960,20 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="4" t="n">
-        <v>0</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H59" s="2" t="n">
         <v>0</v>
@@ -17581,7 +18005,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests</t>
+          <t>fml-c1-wn</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -17638,7 +18062,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>fml-c1-broad - travel interests – copy</t>
+          <t>fml-c1-wn [03-01-26]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -17695,7 +18119,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>fml-c1-wn</t>
+          <t>fml-c2-002 [08-12-25]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -17752,7 +18176,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fml-c1-wn [03-01-26]</t>
+          <t>fml-cbo-test</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -18607,7 +19031,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>fml-c2-002 [08-12-25]</t>
+          <t>{{campaign.name}}</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -18619,20 +19043,16 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>27</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="G78" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>0</v>
@@ -18656,59 +19076,6 @@
         </is>
       </c>
       <c r="M78" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>{{campaign.name}}</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="n">
-        <v>27</v>
-      </c>
-      <c r="E79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="n">
-        <v>0</v>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -18725,7 +19092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18813,7 +19180,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt; </t>
+          <t>-- &gt; --</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -18825,26 +19192,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -18863,14 +19226,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-- &gt; --</t>
+          <t>chatgpt.com &gt; --</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -18882,7 +19245,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -18923,7 +19286,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -18976,7 +19339,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy</t>
+          <t>foremost &gt; --</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -19029,7 +19392,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -19038,51 +19401,45 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>675</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>175.0694459350287</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1.925925925925926</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -19091,31 +19448,31 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D7" t="n">
-        <v>675</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>175.0694459350287</v>
+        <v>187.0189991928975</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.925925925925926</v>
+        <v>4.23728813559322</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>8275.590714285714</v>
@@ -19129,7 +19486,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -19138,31 +19495,31 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>56950.30168970814</v>
       </c>
       <c r="D8" t="n">
-        <v>118</v>
+        <v>329</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>187.0189991928975</v>
+        <v>173.1012209413621</v>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.23728813559322</v>
+        <v>2.43161094224924</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>44995</v>
+        <v>71992</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3617.046428571426</v>
+        <v>5787.274285714288</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>1.08741482157467</v>
+        <v>1.087414821574671</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8.741482157467043</v>
+        <v>8.741482157467054</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>8275.590714285714</v>
@@ -19176,7 +19533,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -19185,25 +19542,25 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>56950.30168970814</v>
+        <v>34526.12039938556</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>210</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>173.1012209413621</v>
+        <v>164.4100971399312</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.43161094224924</v>
+        <v>0.9523809523809524</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>71992</v>
+        <v>17998</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>5787.274285714288</v>
+        <v>1446.818571428572</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>1.087414821574671</v>
@@ -19223,7 +19580,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -19232,45 +19589,51 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>34526.12039938556</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>164.4100971399312</v>
+        <v>212.8549408783784</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.9523809523809524</v>
+        <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J10" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -19279,40 +19642,34 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>387</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>212.8549408783784</v>
+        <v>128.0429721873036</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0</v>
+        <v>1.291989664082687</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -19323,7 +19680,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -19332,45 +19689,51 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>387</v>
+        <v>202</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>128.0429721873036</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.291989664082687</v>
+        <v>1.485148514851485</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J12" s="6" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>10080.81</v>
+        <v>26997</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>26997</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -19382,22 +19745,22 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>202</v>
+        <v>312</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.485148514851485</v>
+        <v>2.243589743589744</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>26997</v>
+        <v>62993</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -19423,7 +19786,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -19435,22 +19798,22 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>312</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>2.243589743589744</v>
+        <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>62993</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>62993</v>
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -19469,14 +19832,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -19488,7 +19851,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -19529,7 +19892,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -19541,22 +19904,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -19575,14 +19938,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -19594,16 +19957,20 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>18</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>5.555555555555555</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
         <v>8999</v>
@@ -19635,7 +20002,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -19647,26 +20014,22 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -19685,14 +20048,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -19704,7 +20067,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -19745,7 +20108,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -19757,7 +20120,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -19798,7 +20161,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -19810,7 +20173,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -19851,7 +20214,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -19863,22 +20226,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>205</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>1.951219512195122</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>35996</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -19897,14 +20260,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
+          <t>{{campaign.name}} &gt; {{adset.name}}</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -19916,22 +20279,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>205</v>
+        <v>27</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.951219512195122</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>35996</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -19949,59 +20312,6 @@
         </is>
       </c>
       <c r="M23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}}</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>27</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -20018,7 +20328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -20106,7 +20416,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> &gt;  &gt; </t>
+          <t>-- &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -20118,26 +20428,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -20156,14 +20462,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>-- &gt; -- &gt; --</t>
+          <t>chatgpt.com &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -20175,7 +20481,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -20216,7 +20522,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>chatgpt.com &gt; -- &gt; --</t>
+          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -20269,7 +20575,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fml-p1-002 &gt; coding languages – copy &gt; abhishekpal-ad 2 hook 6-1;1 ratio-311025-006</t>
+          <t>foremost &gt; -- &gt; --</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -20322,7 +20628,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>foremost &gt; -- &gt; --</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -20331,51 +20637,45 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0</v>
+        <v>118171.8760061444</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>675</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>175.0694459350287</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0</v>
+        <v>1.925925925925926</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>116987</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>9404.320714285714</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.08741482157467</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>8.741482157467049</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; fml &lt;&gt; 01/07 &lt;&gt; it audience &gt; split screen &lt;&gt; germany is actively hiring international talent right now &gt;</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -20384,31 +20684,31 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>118171.8760061444</v>
+        <v>22068.2419047619</v>
       </c>
       <c r="D7" t="n">
-        <v>675</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>175.0694459350287</v>
+        <v>187.0189991928975</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.925925925925926</v>
+        <v>4.23728813559322</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>116987</v>
+        <v>44995</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>9404.320714285714</v>
+        <v>3617.046428571426</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>1.08741482157467</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8.741482157467049</v>
+        <v>8.741482157467043</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>8275.590714285714</v>
@@ -20422,7 +20722,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; it audience rigid – copy &gt; image ad &lt;&gt; sticky note &lt;&gt; join this masterclass, dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -20431,19 +20731,19 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>22068.2419047619</v>
+        <v>28593.79730670763</v>
       </c>
       <c r="D8" t="n">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>187.0189991928975</v>
+        <v>168.1988076865155</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.23728813559322</v>
+        <v>2.941176470588235</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>44995</v>
@@ -20469,7 +20769,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -20478,45 +20778,51 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>28593.79730670763</v>
+        <v>949.1716948284691</v>
       </c>
       <c r="D9" t="n">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>168.1988076865155</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>2.941176470588235</v>
+        <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>3617.046428571426</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>1.08741482157467</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>8.741482157467043</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; if you want a it job abroad in 2026</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -20525,51 +20831,45 @@
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>949.1716948284691</v>
+        <v>27407.33268817205</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>181.5055144912056</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>1.986754966887417</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>26997</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>2170.227857142858</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 3 &gt; what if i get rejected my english not that good &lt;&gt; navy blue blazer</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -20578,45 +20878,51 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>27407.33268817205</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="D11" t="n">
-        <v>151</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>181.5055144912056</v>
+        <v>118.6464618535586</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.986754966887417</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>2170.227857142858</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; laptop screen | if you're an it professional in india &amp; looking to get</t>
+          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -20625,51 +20931,45 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>34407.47393753201</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>209</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>118.6464618535586</v>
+        <v>164.629061902067</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0</v>
+        <v>0.9569377990430622</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>17998</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1446.818571428572</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.087414821574671</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>8.741482157467054</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>8275.590714285714</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; 01/07 &lt;&gt; abo &gt; software developer interests – copy 4 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -20678,45 +20978,51 @@
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>34407.47393753201</v>
+        <v>851.4197635135137</v>
       </c>
       <c r="D13" t="n">
-        <v>209</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>164.629061902067</v>
+        <v>212.8549408783784</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.9569377990430622</v>
+        <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>1446.818571428572</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>1.087414821574671</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>8.741482157467054</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>8275.590714285714</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 2 &gt; faceless &lt;&gt; writing on table | so europe is hiring it professionals</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -20725,40 +21031,34 @@
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>851.4197635135137</v>
+        <v>49552.63023648649</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>387</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>212.8549408783784</v>
+        <v>128.0429721873036</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0</v>
+        <v>1.291989664082687</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>44995</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>-5409.050000000003</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>0.8926862027952118</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>-10.73137972047882</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>10080.81</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -20769,7 +21069,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; multi format | 8572 &gt; software developer interests – copy 3 &gt; faceless &lt;&gt; writing on table | if you're this an it professional with 2 +</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -20778,34 +21078,40 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>49552.63023648649</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>387</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>128.0429721873036</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.291989664082687</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>44995</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>-5409.050000000003</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>0.8926862027952118</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>-10.73137972047882</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>10080.81</v>
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -20816,7 +21122,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; --</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -20828,22 +21134,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>1.492537313432836</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -20862,14 +21168,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -20881,22 +21187,22 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>201</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.492537313432836</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -20915,14 +21221,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -20934,22 +21240,22 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>311</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>2.2508038585209</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>62993</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>62993</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -20968,14 +21274,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20987,22 +21293,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>311</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.2508038585209</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>62993</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>62993</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -21021,14 +21327,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -21040,7 +21346,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -21081,7 +21387,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -21134,7 +21440,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -21146,7 +21452,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -21187,7 +21493,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -21199,22 +21505,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -21233,14 +21539,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -21252,16 +21558,20 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="4" t="n">
-        <v>50</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H24" s="2" t="n">
         <v>8999</v>
@@ -21293,7 +21603,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -21305,26 +21615,22 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I25" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -21343,14 +21649,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -21362,7 +21668,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -21403,7 +21709,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -21415,7 +21721,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
@@ -21456,7 +21762,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -21468,7 +21774,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
@@ -21509,7 +21815,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -21521,7 +21827,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -21562,7 +21868,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -21574,7 +21880,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>0</v>
@@ -21615,7 +21921,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -21627,22 +21933,22 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0</v>
+        <v>7.894736842105263</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -21661,14 +21967,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -21680,22 +21986,22 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>7.894736842105263</v>
+        <v>0.5988023952095809</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>26997</v>
+        <v>8999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -21721,7 +22027,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
+          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -21733,22 +22039,22 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>167</v>
+        <v>27</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.5988023952095809</v>
+        <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -21766,59 +22072,6 @@
         </is>
       </c>
       <c r="M33" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>27</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -21835,14 +22088,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Raw Meta Spend</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>282120.59</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Attributed Spend</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>282120.59</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unallocated Spend</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21855,14 +22148,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Funnel Stage</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Total Leads</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2589</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Paid Leads</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2542</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unpaid Leads</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/satyam_7d.xlsx
+++ b/output/satyam_7d.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3795</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="14">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3712</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="15">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>97.8129117259552</v>
+        <v>98.00976342470898</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.187088274044796</v>
+        <v>1.990236575291025</v>
       </c>
     </row>
     <row r="18">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3715</v>
+        <v>2613</v>
       </c>
     </row>
     <row r="19">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
@@ -1584,7 +1584,7 @@
   <dimension ref="A1:AB71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
@@ -1757,8 +1757,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
-        <v>46242</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -1854,8 +1856,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
-        <v>46242</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1951,8 +1955,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
-        <v>46242</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2048,8 +2054,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46242</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2145,8 +2153,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
-        <v>46242</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -2242,8 +2252,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>46242</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -2339,8 +2351,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>46242</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -2436,8 +2450,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>46242</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -2533,8 +2549,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>46242</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2630,8 +2648,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>46242</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2727,8 +2747,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
-        <v>46242</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2824,8 +2846,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>46242</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2921,8 +2945,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
-        <v>46242</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -3018,8 +3044,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>46242</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -3115,8 +3143,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
-        <v>46242</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3212,8 +3242,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46242</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3309,8 +3341,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>46242</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3406,8 +3440,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>46242</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3503,8 +3539,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>46242</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3600,8 +3638,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>46242</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3697,8 +3737,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46242</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3794,8 +3836,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>46242</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3896,8 +3940,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>46242</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3993,8 +4039,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>46242</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4090,8 +4138,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>46242</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4192,8 +4242,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46242</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4289,8 +4341,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>46242</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -4386,8 +4440,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>46242</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -4483,8 +4539,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>46242</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4580,8 +4638,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>46242</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4677,8 +4737,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46242</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4774,8 +4836,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>46242</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4871,8 +4935,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>46242</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4968,8 +5034,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>46242</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -5065,8 +5133,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>46242</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -5162,8 +5232,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>46242</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -5259,8 +5331,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
-        <v>46242</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5356,8 +5430,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
-        <v>46242</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5453,8 +5529,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
-        <v>46242</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5550,8 +5628,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
-        <v>46242</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -5647,8 +5727,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
-        <v>46242</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5744,8 +5826,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
-        <v>46242</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5841,8 +5925,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
-        <v>46242</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5938,8 +6024,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
-        <v>46242</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -6035,8 +6123,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
-        <v>46242</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -6132,8 +6222,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
-        <v>46242</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -6229,8 +6321,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
-        <v>46242</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6326,8 +6420,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
-        <v>46242</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6423,8 +6519,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
-        <v>46242</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6520,8 +6618,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
-        <v>46242</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6617,8 +6717,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
-        <v>46242</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6714,8 +6816,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
-        <v>46242</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6811,8 +6915,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
-        <v>46242</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -6908,8 +7014,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
-        <v>46242</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -7005,8 +7113,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
-        <v>46242</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -7102,8 +7212,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
-        <v>46242</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -7199,8 +7311,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
-        <v>46242</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -7296,8 +7410,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
-        <v>46242</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -7393,8 +7509,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
-        <v>46242</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -7490,8 +7608,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
-        <v>46242</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7587,8 +7707,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
-        <v>46242</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -7684,8 +7806,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
-        <v>46242</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -7781,8 +7905,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
-        <v>46242</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -7878,8 +8004,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
-        <v>46242</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -7975,8 +8103,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
-        <v>46242</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8072,8 +8202,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
-        <v>46242</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -8169,8 +8301,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
-        <v>46242</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -8266,8 +8400,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
-        <v>46242</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -8363,8 +8499,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
-        <v>46242</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -8460,8 +8598,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
-        <v>46242</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -8810,10 +8950,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3795</v>
+        <v>2663</v>
       </c>
       <c r="D9" t="n">
-        <v>3795</v>
+        <v>2663</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15398,16 +15538,16 @@
         <v>231716.54</v>
       </c>
       <c r="D2" t="n">
-        <v>1992</v>
+        <v>1367</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>169.5073445501097</v>
       </c>
       <c r="F2" t="n">
         <v>28</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>1.405622489959839</v>
+        <v>2.04828090709583</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>251972</v>
@@ -15445,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>732</v>
+        <v>534</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -15454,7 +15594,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1.229508196721312</v>
+        <v>1.685393258426966</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>80991</v>
@@ -15498,16 +15638,16 @@
         <v>50404.05</v>
       </c>
       <c r="D4" t="n">
-        <v>598</v>
+        <v>397</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>126.9623425692695</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.8361204013377926</v>
+        <v>1.259445843828715</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>44995</v>
@@ -15545,7 +15685,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>0</v>
@@ -15554,7 +15694,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.646090534979424</v>
+        <v>1.895734597156398</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>35996</v>
@@ -15598,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>0</v>
@@ -15607,7 +15747,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>8999</v>
@@ -15651,7 +15791,7 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -15660,7 +15800,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.666666666666667</v>
+        <v>3.125</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>8999</v>
@@ -15704,16 +15844,20 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="4" t="n">
-        <v>5.555555555555555</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H8" s="2" t="n">
         <v>8999</v>
@@ -19674,7 +19818,7 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>0</v>
@@ -19723,7 +19867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -19823,7 +19967,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -19832,7 +19976,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
@@ -20035,16 +20179,16 @@
         <v>118068.4177208835</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
+        <v>691</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>170.8660169622048</v>
       </c>
       <c r="F6" t="n">
         <v>13</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.280788177339901</v>
+        <v>1.881331403762663</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>116987</v>
@@ -20082,16 +20226,16 @@
         <v>22334.1243373494</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>180.1139059463661</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.604166666666667</v>
+        <v>4.032258064516129</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>44995</v>
@@ -20129,16 +20273,16 @@
         <v>56765.89935742972</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>337</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>168.444805214925</v>
       </c>
       <c r="F8" t="n">
         <v>8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.639344262295082</v>
+        <v>2.373887240356083</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>71992</v>
@@ -20176,16 +20320,16 @@
         <v>34548.09858433735</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>215</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>160.6888306248249</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6734006734006733</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>17998</v>
@@ -20223,10 +20367,10 @@
         <v>842.8770903010034</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>84.28770903010033</v>
+        <v>210.7192725752508</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -20272,16 +20416,16 @@
         <v>49561.172909699</v>
       </c>
       <c r="D11" t="n">
-        <v>588</v>
+        <v>393</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>126.1098547320585</v>
       </c>
       <c r="F11" t="n">
         <v>5</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.8503401360544218</v>
+        <v>1.272264631043257</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>44995</v>
@@ -20319,7 +20463,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>288</v>
+        <v>209</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -20328,7 +20472,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.041666666666667</v>
+        <v>1.435406698564593</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>26997</v>
@@ -20372,7 +20516,7 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>444</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -20381,7 +20525,7 @@
         <v>6</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.351351351351351</v>
+        <v>1.846153846153846</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>53994</v>
@@ -20425,7 +20569,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>0</v>
@@ -20478,7 +20622,7 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -20531,7 +20675,7 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -20540,7 +20684,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>8999</v>
@@ -20584,16 +20728,20 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="4" t="n">
-        <v>9.090909090909092</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H17" s="2" t="n">
         <v>8999</v>
@@ -20625,7 +20773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -20637,7 +20785,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
@@ -20678,7 +20826,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -20690,7 +20838,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
@@ -20731,7 +20879,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -20743,7 +20891,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -20784,7 +20932,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 |</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -20796,7 +20944,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -20837,7 +20985,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 |</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -20849,22 +20997,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0</v>
+        <v>1.895734597156398</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>35996</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>35996</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -20883,14 +21031,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open</t>
+          <t>{{campaign.name}} &gt; {{adset.name}}</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -20902,22 +21050,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>243</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.646090534979424</v>
+        <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>35996</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>35996</v>
+        <v>0</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -20935,59 +21083,6 @@
         </is>
       </c>
       <c r="M23" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}}</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>51</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -21004,7 +21099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M39"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -21104,7 +21199,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -21113,7 +21208,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
@@ -21316,16 +21411,16 @@
         <v>118068.4177208835</v>
       </c>
       <c r="D6" t="n">
-        <v>1015</v>
+        <v>691</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>170.8660169622048</v>
       </c>
       <c r="F6" t="n">
         <v>13</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.280788177339901</v>
+        <v>1.881331403762663</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>116987</v>
@@ -21363,16 +21458,16 @@
         <v>22334.1243373494</v>
       </c>
       <c r="D7" t="n">
-        <v>192</v>
+        <v>124</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>180.1139059463661</v>
       </c>
       <c r="F7" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.604166666666667</v>
+        <v>4.032258064516129</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>44995</v>
@@ -21410,16 +21505,16 @@
         <v>28150.3025502008</v>
       </c>
       <c r="D8" t="n">
-        <v>242</v>
+        <v>171</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>164.6216523403556</v>
       </c>
       <c r="F8" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2.066115702479339</v>
+        <v>2.923976608187134</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>44995</v>
@@ -21506,16 +21601,16 @@
         <v>27452.36116465864</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>156</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>175.9766741324271</v>
       </c>
       <c r="F10" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.271186440677966</v>
+        <v>1.923076923076923</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>26997</v>
@@ -21602,16 +21697,16 @@
         <v>34431.77502008032</v>
       </c>
       <c r="D12" t="n">
-        <v>296</v>
+        <v>214</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>160.8961449536464</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.6756756756756757</v>
+        <v>0.9345794392523363</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>17998</v>
@@ -21649,10 +21744,10 @@
         <v>842.8770903010034</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>84.28770903010033</v>
+        <v>210.7192725752508</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -21698,16 +21793,16 @@
         <v>49561.172909699</v>
       </c>
       <c r="D14" t="n">
-        <v>588</v>
+        <v>393</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>126.1098547320585</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.8503401360544218</v>
+        <v>1.272264631043257</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>44995</v>
@@ -21786,7 +21881,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt; – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -21798,22 +21893,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>208</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0</v>
+        <v>1.442307692307692</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -21832,14 +21927,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; it &amp; technical services &gt; foremostleads-gs-13-09&lt;attention it professionals if you are an it engineer&gt; – copy</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -21851,22 +21946,22 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>286</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.048951048951049</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>26997</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -21885,14 +21980,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremost leads-13-09&lt;do you know which countries are hiring&gt; – copy 2</t>
+          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -21904,22 +21999,22 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>324</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0</v>
+        <v>1.851851851851852</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>53994</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>53994</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -21938,14 +22033,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>foremost leads &lt;&gt; cbo &lt;&gt; r1 &gt; foremost leads &lt;&gt; a1&lt;&gt; programming language &gt; foremostleads-gs-13-09&lt;do you know which countries are actively sponsoring visas&gt; – copy 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -21957,22 +22052,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>443</v>
+        <v>2</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.354401805869075</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>53994</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>53994</v>
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -21991,14 +22086,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 10</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -22010,7 +22105,7 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
@@ -22051,7 +22146,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; data science | 30 -55 &gt; split ad 4</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -22063,7 +22158,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>0</v>
@@ -22104,7 +22199,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 1</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -22116,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>0</v>
@@ -22157,7 +22252,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 2</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -22169,22 +22264,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -22203,14 +22298,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; information technology | 30 -55 &gt; split ad 3</t>
+          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -22222,22 +22317,26 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -22256,14 +22355,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 5</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -22275,7 +22374,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -22316,7 +22415,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 6</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -22328,7 +22427,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -22369,7 +22468,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; software engineering | 30 -55 &gt; split ad 7</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -22381,22 +22480,22 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>33.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -22415,14 +22514,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 1</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -22434,7 +22533,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
@@ -22475,7 +22574,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; cloud &amp; data professionals | 25 - 55 &gt; abhishek pal 2</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -22487,22 +22586,22 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -22521,14 +22620,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; core it professionals | 25 - 55 &gt; abhishek pal 5</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -22540,7 +22639,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>0</v>
@@ -22581,7 +22680,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | dubai's tech sector is growing fast and sponsoring visas now</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -22593,22 +22692,22 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>0</v>
+        <v>26997</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>26997</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -22627,14 +22726,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; c++ | 26 - 50 | &gt; image ads | sticky notes | stop applying to places that were never going to sponsor you. find out who actually does</t>
+          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -22646,22 +22745,22 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0</v>
+        <v>0.5847953216374269</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -22680,14 +22779,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; data science &amp; big data &amp; data analyst | 26 - 50 | &gt; image ads | whiteboard | pick the right country for your experience. not just what's trending</t>
+          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -22699,7 +22798,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0</v>
@@ -22732,324 +22831,6 @@
         </is>
       </c>
       <c r="M33" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | sticky notes | germany is short on tech workers and hiring from india right now</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>7</v>
-      </c>
-      <c r="E34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; java &amp; java script | 26 - 50 | &gt; image ads | whiteboard | know what dutch companies look for before you apply</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; web development | 26 - 50 | &gt; image ads | ignored vs shortlisted</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>27</v>
-      </c>
-      <c r="E36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504(1).mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>72</v>
-      </c>
-      <c r="E37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>4.166666666666666</v>
-      </c>
-      <c r="H37" s="2" t="n">
-        <v>26997</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>26997</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; foremostleads-gs-13-09-open &gt; foremostleads-gs-13-09- ai video &lt;0504.mp4&gt;</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>171</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>0.5847953216374269</v>
-      </c>
-      <c r="H38" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I38" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{adset.name}} &gt; {{ad.name}}</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>51</v>
-      </c>
-      <c r="E39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -23066,13 +22847,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="7" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -23166,7 +22947,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0</v>
@@ -23175,7 +22956,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>5.263157894736842</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>8999</v>
@@ -23427,10 +23208,10 @@
         <v>465.2942570281124</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>232.6471285140562</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -23476,10 +23257,10 @@
         <v>3955.001184738956</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>164.7917160307898</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -23525,16 +23306,16 @@
         <v>12446.62137550201</v>
       </c>
       <c r="D9" t="n">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>159.5720689166924</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>1.869158878504673</v>
+        <v>2.564102564102564</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>17998</v>
@@ -23572,10 +23353,10 @@
         <v>697.9413855421687</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>232.6471285140562</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -23621,16 +23402,16 @@
         <v>25940.15482931727</v>
       </c>
       <c r="D11" t="n">
-        <v>223</v>
+        <v>140</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>185.2868202094091</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.345291479820628</v>
+        <v>2.142857142857143</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>26997</v>
@@ -23668,16 +23449,16 @@
         <v>170297.6980722892</v>
       </c>
       <c r="D12" t="n">
-        <v>1464</v>
+        <v>1017</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>167.45103055289</v>
       </c>
       <c r="F12" t="n">
         <v>22</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.502732240437158</v>
+        <v>2.16322517207473</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>197978</v>
@@ -23715,16 +23496,16 @@
         <v>14540.44553212851</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>177.3225064893721</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.8</v>
+        <v>1.219512195121951</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>8999</v>
@@ -23762,10 +23543,10 @@
         <v>2675.441977911647</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>157.3789398771557</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -23811,16 +23592,20 @@
         <v>232.6471285140562</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>116.3235642570281</v>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="4" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H15" s="2" t="n">
         <v>0</v>
@@ -23909,10 +23694,10 @@
         <v>674.3016722408028</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>96.32881032011468</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -23958,16 +23743,16 @@
         <v>2444.34356187291</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>111.1065255396777</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.448275862068965</v>
+        <v>4.545454545454546</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>8999</v>
@@ -24054,10 +23839,10 @@
         <v>2612.918979933111</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>124.4247133301481</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -24103,16 +23888,16 @@
         <v>43576.74556856188</v>
       </c>
       <c r="D21" t="n">
-        <v>517</v>
+        <v>338</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>128.9252827472245</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.7736943907156674</v>
+        <v>1.183431952662722</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>35996</v>
@@ -24150,10 +23935,10 @@
         <v>758.5893812709031</v>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>126.4315635451505</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -24199,10 +23984,10 @@
         <v>168.5754180602007</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>84.28770903010034</v>
+        <v>168.5754180602007</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -24301,7 +24086,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>0</v>
@@ -24310,7 +24095,7 @@
         <v>1</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.333333333333333</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>8999</v>
@@ -24354,7 +24139,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>0</v>
@@ -24363,7 +24148,7 @@
         <v>3</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.851851851851852</v>
+        <v>2.830188679245283</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>26997</v>
@@ -24407,7 +24192,7 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>0</v>
@@ -24460,7 +24245,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
@@ -24469,7 +24254,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>1.01010101010101</v>
+        <v>1.282051282051282</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>8999</v>
@@ -24513,7 +24298,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>378</v>
+        <v>285</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>0</v>
@@ -24522,7 +24307,7 @@
         <v>2</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.5291005291005291</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>17998</v>
@@ -24566,7 +24351,7 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>0</v>
@@ -24619,7 +24404,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E31" s="2" t="n">
         <v>0</v>
@@ -24628,7 +24413,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.272727272727273</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>8999</v>
@@ -24713,7 +24498,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_instream_video</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -24725,7 +24510,7 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>0</v>
@@ -24766,7 +24551,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_feed</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -24778,7 +24563,7 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>0</v>
@@ -24819,7 +24604,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; facebook_mobile_reels</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -24831,22 +24616,22 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -24865,14 +24650,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_feed</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -24884,22 +24669,22 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -24918,14 +24703,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_reels</t>
+          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -24937,7 +24722,7 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>0</v>
@@ -24978,7 +24763,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 11th august 2026 &gt; instagram_stories</t>
+          <t>foremost leads | cbo | 14th august &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -24990,22 +24775,26 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -25024,14 +24813,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; facebook_instream_video</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -25043,7 +24832,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>0</v>
@@ -25084,7 +24873,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; facebook_mobile_reels</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -25096,7 +24885,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>0</v>
@@ -25137,7 +24926,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_feed</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -25149,7 +24938,7 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>0</v>
@@ -25190,7 +24979,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_reels</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -25202,7 +24991,7 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>0</v>
@@ -25243,7 +25032,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 14th august &gt; instagram_stories</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -25255,22 +25044,22 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>8999</v>
+        <v>0</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -25289,14 +25078,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_feed</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; others</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -25308,7 +25097,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>0</v>
@@ -25349,7 +25138,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; facebook_mobile_reels</t>
+          <t>foremost leads | cbo | 5th aug 2026 &gt; threads_feed</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -25361,7 +25150,7 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>0</v>
@@ -25402,7 +25191,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_feed</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_desktop_feed</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -25414,7 +25203,7 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>0</v>
@@ -25455,7 +25244,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_reels</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_instream_video</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -25467,7 +25256,7 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>0</v>
@@ -25508,7 +25297,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; instagram_stories</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_mobile_feed</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -25520,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>0</v>
@@ -25561,7 +25350,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; others</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_mobile_reels</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -25573,7 +25362,7 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>0</v>
@@ -25614,7 +25403,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>foremost leads | cbo | 5th aug 2026 &gt; threads_feed</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_notification</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -25626,16 +25415,20 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="F50" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="4" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="H50" s="2" t="n">
         <v>0</v>
@@ -25667,7 +25460,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_desktop_feed</t>
+          <t>foremostleads-gs-13-09 &gt; facebook_stories</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -25679,7 +25472,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>0</v>
@@ -25720,7 +25513,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_instream_video</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_feed</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -25732,22 +25525,22 @@
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -25766,14 +25559,14 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_mobile_feed</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_reels</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -25785,22 +25578,22 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>136</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0</v>
+        <v>1.470588235294118</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+        <v>17998</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>17998</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -25819,14 +25612,14 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_mobile_reels</t>
+          <t>foremostleads-gs-13-09 &gt; instagram_stories</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -25838,22 +25631,22 @@
         <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>8999</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>8999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -25872,14 +25665,14 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_notification</t>
+          <t>{{campaign.name}} &gt; {{placement}}</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -25891,7 +25684,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>0</v>
@@ -25924,271 +25717,6 @@
         </is>
       </c>
       <c r="M55" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; facebook_stories</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>4</v>
-      </c>
-      <c r="E56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_feed</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
-        <v>24</v>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>4.166666666666666</v>
-      </c>
-      <c r="H57" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_reels</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>149</v>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>1.342281879194631</v>
-      </c>
-      <c r="H58" s="2" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>17998</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>foremostleads-gs-13-09 &gt; instagram_stories</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="n">
-        <v>30</v>
-      </c>
-      <c r="E59" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="H59" s="2" t="n">
-        <v>8999</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>8999</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>{{campaign.name}} &gt; {{placement}}</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="n">
-        <v>51</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -26291,7 +25819,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3795</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="3">
@@ -26301,7 +25829,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3712</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="4">
@@ -26311,7 +25839,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
